--- a/artfynd/A 34009-2021 artfynd.xlsx
+++ b/artfynd/A 34009-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119674141</v>
+        <v>119674144</v>
       </c>
       <c r="B2" t="n">
         <v>90562</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541251</v>
+        <v>541143</v>
       </c>
       <c r="R2" t="n">
-        <v>6682318</v>
+        <v>6682326</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119674140</v>
+        <v>119674143</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541277</v>
+        <v>541247</v>
       </c>
       <c r="R3" t="n">
-        <v>6682319</v>
+        <v>6682342</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119674143</v>
+        <v>119674140</v>
       </c>
       <c r="B4" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541247</v>
+        <v>541277</v>
       </c>
       <c r="R4" t="n">
-        <v>6682342</v>
+        <v>6682319</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119674144</v>
+        <v>119674141</v>
       </c>
       <c r="B6" t="n">
         <v>90562</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541143</v>
+        <v>541251</v>
       </c>
       <c r="R6" t="n">
-        <v>6682326</v>
+        <v>6682318</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 34009-2021 artfynd.xlsx
+++ b/artfynd/A 34009-2021 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119674143</v>
+        <v>119674142</v>
       </c>
       <c r="B3" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541247</v>
+        <v>541254</v>
       </c>
       <c r="R3" t="n">
-        <v>6682342</v>
+        <v>6682328</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119674142</v>
+        <v>119674143</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541254</v>
+        <v>541247</v>
       </c>
       <c r="R5" t="n">
-        <v>6682328</v>
+        <v>6682342</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 34009-2021 artfynd.xlsx
+++ b/artfynd/A 34009-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119674144</v>
+        <v>119674140</v>
       </c>
       <c r="B2" t="n">
         <v>90562</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>541143</v>
+        <v>541277</v>
       </c>
       <c r="R2" t="n">
-        <v>6682326</v>
+        <v>6682319</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119674142</v>
+        <v>119674143</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>90527</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541254</v>
+        <v>541247</v>
       </c>
       <c r="R3" t="n">
-        <v>6682328</v>
+        <v>6682342</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119674140</v>
+        <v>119674141</v>
       </c>
       <c r="B4" t="n">
         <v>90562</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541277</v>
+        <v>541251</v>
       </c>
       <c r="R4" t="n">
-        <v>6682319</v>
+        <v>6682318</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119674143</v>
+        <v>119674142</v>
       </c>
       <c r="B5" t="n">
-        <v>90527</v>
+        <v>90562</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541247</v>
+        <v>541254</v>
       </c>
       <c r="R5" t="n">
-        <v>6682342</v>
+        <v>6682328</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119674141</v>
+        <v>119674144</v>
       </c>
       <c r="B6" t="n">
         <v>90562</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541251</v>
+        <v>541143</v>
       </c>
       <c r="R6" t="n">
-        <v>6682318</v>
+        <v>6682326</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>

--- a/artfynd/A 34009-2021 artfynd.xlsx
+++ b/artfynd/A 34009-2021 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>119674140</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119674143</v>
+        <v>119674141</v>
       </c>
       <c r="B3" t="n">
-        <v>90527</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>541247</v>
+        <v>541251</v>
       </c>
       <c r="R3" t="n">
-        <v>6682342</v>
+        <v>6682318</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119674141</v>
+        <v>119674142</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>541251</v>
+        <v>541254</v>
       </c>
       <c r="R4" t="n">
-        <v>6682318</v>
+        <v>6682328</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,15 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119674142</v>
+        <v>119674144</v>
       </c>
       <c r="B5" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1021,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>541254</v>
+        <v>541143</v>
       </c>
       <c r="R5" t="n">
-        <v>6682328</v>
+        <v>6682326</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,37 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119674144</v>
+        <v>119674143</v>
       </c>
       <c r="B6" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>541143</v>
+        <v>541247</v>
       </c>
       <c r="R6" t="n">
-        <v>6682326</v>
+        <v>6682342</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
